--- a/testdata/realdata/olts.xlsx
+++ b/testdata/realdata/olts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,11 @@
           <t>PON口数</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -459,6 +464,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -481,6 +491,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -503,6 +518,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -525,6 +545,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -545,6 +570,11 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>在网</t>
         </is>
       </c>
     </row>

--- a/testdata/realdata/olts.xlsx
+++ b/testdata/realdata/olts.xlsx
@@ -446,12 +446,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OLT-279116876</t>
+          <t>OLT-244077958</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MR279116876</t>
+          <t>MR244077958</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -473,12 +473,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OLT-244077958</t>
+          <t>OLT-244081515</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MR244077958</t>
+          <t>MR244081515</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,12 +500,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OLT-244081515</t>
+          <t>OLT-279116876</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MR244081515</t>
+          <t>MR279116876</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,12 +527,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OLT-4059698545</t>
+          <t>OLT-304758391</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MR4059698545</t>
+          <t>MR304758391</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,12 +554,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OLT-304758391</t>
+          <t>OLT-4059698545</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MR304758391</t>
+          <t>MR4059698545</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
